--- a/data/excel/ot_checklists.xlsx
+++ b/data/excel/ot_checklists.xlsx
@@ -38,6 +38,36 @@
   </x:si>
   <x:si>
     <x:t>CompletadoPor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TemplateCode</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TipoRespuesta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Respuesta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ValorNumerico</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EvidenciaId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiereFoto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiereArchivo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiereFirma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FirmaId</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -414,9 +444,19 @@
     <x:col min="6" max="6" width="11.853482" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="17.424911" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="15.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.996339" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.139196" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="5.710625" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="13.139196" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="15.567768" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13.996339" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="7.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
+    <x:row r="1" spans="1:18">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -440,6 +480,36 @@
       </x:c>
       <x:c r="H1" s="1" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M1" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N1" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O1" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P1" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q1" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R1" s="1" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
